--- a/metadata/corpus_metadata_v2.xlsx
+++ b/metadata/corpus_metadata_v2.xlsx
@@ -762,7 +762,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       編者が補った値であり，先生のご確認をお願いしたい。</t>
+          <t xml:space="preserve">                       編者が補った値であり，確認を要する。</t>
         </is>
       </c>
     </row>
